--- a/tools/importer/reports/import-nav.report.xlsx
+++ b/tools/importer/reports/import-nav.report.xlsx
@@ -67,7 +67,7 @@
     <t>nav</t>
   </si>
   <si>
-    <t>2026-09-29T20:27:01.361Z</t>
+    <t>2026-09-29T21:03:36.050Z</t>
   </si>
   <si>
     <t>http://127.0.0.1:8765/nav.html</t>
@@ -82,7 +82,7 @@
     <t>innovationlabgt/bronco</t>
   </si>
   <si>
-    <t>2026-09-29T20:16:57.195Z</t>
+    <t>2026-09-29T21:03:29.578Z</t>
   </si>
 </sst>
 </file>
